--- a/data/precios_objetivo.xlsx
+++ b/data/precios_objetivo.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2380</v>
+        <v>2140</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>333.48</v>
+        <v>312.605</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>404.90475</v>
+        <v>397.2857</v>
       </c>
       <c r="G4" t="n">
         <v>347</v>
       </c>
       <c r="H4" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="I4" t="n">
         <v>21</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2850</v>
+        <v>2420</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>41.21</v>
+        <v>39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>326</v>
+        <v>262.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -711,20 +711,20 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>465</v>
+        <v>385</v>
       </c>
       <c r="G7" t="n">
-        <v>465</v>
+        <v>385</v>
       </c>
       <c r="H7" t="n">
-        <v>465</v>
+        <v>385</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.345</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>13.13571</v>
+        <v>13.4</v>
       </c>
       <c r="G8" t="n">
         <v>10.5</v>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>261.5</v>
+        <v>243</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>390</v>
+        <v>390.5</v>
       </c>
       <c r="G9" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H9" t="n">
         <v>420</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.85</v>
+        <v>20.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>37.4051</v>
+        <v>40.0227</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3725</v>
+        <v>3005</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64.8</v>
+        <v>78</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.2</v>
+        <v>35.545</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>67.9742</v>
+        <v>66.5742</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>564</v>
+        <v>533</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>198.67</v>
+        <v>160.555</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>238.5</v>
+        <v>238.08109</v>
       </c>
       <c r="G17" t="n">
         <v>188</v>
@@ -1164,7 +1164,7 @@
         <v>301</v>
       </c>
       <c r="I17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23.41</v>
+        <v>20.422</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.4201</v>
+        <v>0.3507</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>840</v>
+        <v>822.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>674</v>
+        <v>657.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>87.78</v>
+        <v>84.37</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1411,16 +1411,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>107.8</v>
+        <v>107.34615</v>
       </c>
       <c r="G23" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H23" t="n">
         <v>120</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4.16</v>
+        <v>3.65</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.97655</v>
+        <v>4.24322</v>
       </c>
       <c r="G24" t="n">
         <v>3.52966</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>471</v>
+        <v>431</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>144.8</v>
+        <v>136.215</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>142.23174</v>
+        <v>144.99261</v>
       </c>
       <c r="G26" t="n">
         <v>72</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3285</v>
+        <v>3315</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>217.12</v>
+        <v>230.15</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>323.41898</v>
+        <v>327.7</v>
       </c>
       <c r="G28" t="n">
         <v>180</v>
@@ -1644,7 +1644,7 @@
         <v>515</v>
       </c>
       <c r="I28" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>860</v>
+        <v>750</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>253.89</v>
+        <v>247.54</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>327.6707</v>
+        <v>329.97787</v>
       </c>
       <c r="G30" t="n">
         <v>230</v>
@@ -1732,7 +1732,7 @@
         <v>405</v>
       </c>
       <c r="I30" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.785</v>
+        <v>11.8187</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>24.01</v>
+        <v>23.81</v>
       </c>
       <c r="G31" t="n">
         <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I31" t="n">
         <v>5</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1841</v>
+        <v>1815</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>141.6</v>
+        <v>149.063</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1859,16 +1859,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>171.14894</v>
+        <v>172.77083</v>
       </c>
       <c r="G33" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H33" t="n">
         <v>220</v>
       </c>
       <c r="I33" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7.92</v>
+        <v>9.045</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9.71429</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="H34" t="n">
         <v>13</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.205</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1255</v>
+        <v>1205</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>765.725</v>
+        <v>764.35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2970</v>
+        <v>2610</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8.880000000000001</v>
+        <v>6.74</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792</v>
+        <v>1780</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.1201</v>
+        <v>3.395</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2233,13 +2233,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7.3793902</v>
+        <v>6.309085</v>
       </c>
       <c r="G42" t="n">
-        <v>4.0552907</v>
+        <v>3.9104602</v>
       </c>
       <c r="H42" t="n">
-        <v>10.095529</v>
+        <v>10.112558</v>
       </c>
       <c r="I42" t="n">
         <v>24</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2336</v>
+        <v>2367</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1815</v>
+        <v>1605</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>290.675</v>
+        <v>333.74</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>371.19354</v>
+        <v>373.7742</v>
       </c>
       <c r="G45" t="n">
         <v>290</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4270</v>
+        <v>3740</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5240</v>
+        <v>4957.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>8700</v>
+        <v>8705.666999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>6500</v>
+        <v>6517</v>
       </c>
       <c r="H47" t="n">
         <v>12300</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1750</v>
+        <v>1650</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1830</v>
+        <v>1714</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>94.965</v>
+        <v>92.11</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1755</v>
+        <v>1665</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.425</v>
+        <v>12.088</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="G52" t="n">
         <v>20</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5.37</v>
+        <v>4.34</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6.979</v>
+        <v>6.699</v>
       </c>
       <c r="G53" t="n">
         <v>4</v>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1610</v>
+        <v>1400</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.6897</v>
+        <v>1.545</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2801,20 +2801,20 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="G55" t="n">
         <v>1.5</v>
       </c>
       <c r="H55" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>underperform</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>80.98999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>93.66</v>
+        <v>92.81556</v>
       </c>
       <c r="G56" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H56" t="n">
         <v>135</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>144.8807</v>
+        <v>192.6401</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2897,16 +2897,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>110.35294</v>
+        <v>120.66667</v>
       </c>
       <c r="G57" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H57" t="n">
         <v>170</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.44</v>
+        <v>11.0538</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2945,20 +2945,20 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>8.81818</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G58" t="n">
         <v>6</v>
       </c>
       <c r="H58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>underperform</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1478</v>
+        <v>2230</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9210</v>
+        <v>8140</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3033,16 +3033,16 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>20500</v>
+        <v>15865</v>
       </c>
       <c r="G60" t="n">
-        <v>20500</v>
+        <v>11230</v>
       </c>
       <c r="H60" t="n">
         <v>20500</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4.655</v>
+        <v>5.57</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>231.04</v>
+        <v>300.335</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3129,16 +3129,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>252.082</v>
+        <v>263.0357</v>
       </c>
       <c r="G62" t="n">
-        <v>135.5</v>
+        <v>165</v>
       </c>
       <c r="H62" t="n">
         <v>330</v>
       </c>
       <c r="I62" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3190</v>
+        <v>3520</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>183.325</v>
+        <v>196.29</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4680</v>
+        <v>4782.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>364.19</v>
+        <v>347.38</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3293,16 +3293,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>525.97394</v>
+        <v>531.8468</v>
       </c>
       <c r="G66" t="n">
         <v>215.88</v>
       </c>
       <c r="H66" t="n">
-        <v>675</v>
+        <v>715</v>
       </c>
       <c r="I66" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>69.01049999999999</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>335.81</v>
+        <v>339.57</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>428.06668</v>
+        <v>429.36295</v>
       </c>
       <c r="G68" t="n">
         <v>340</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>189.935</v>
+        <v>187.815</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>190.74129</v>
+        <v>205.3942</v>
       </c>
       <c r="G69" t="n">
-        <v>107.98</v>
+        <v>145</v>
       </c>
       <c r="H69" t="n">
         <v>480</v>
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>24.865</v>
+        <v>23.415</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>105.22</v>
+        <v>111.6365</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3521,16 +3521,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>121.50538</v>
+        <v>131.44963</v>
       </c>
       <c r="G71" t="n">
         <v>57</v>
       </c>
       <c r="H71" t="n">
-        <v>163.6</v>
+        <v>170</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>52.22</v>
+        <v>48.22</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>18.465</v>
+        <v>20.24</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>111.84</v>
+        <v>94.44</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>155.28857</v>
+        <v>155.11</v>
       </c>
       <c r="G74" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H74" t="n">
         <v>195</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>21.515</v>
+        <v>18.685</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>28.99333</v>
+        <v>29.05029</v>
       </c>
       <c r="G75" t="n">
         <v>22</v>
@@ -3698,7 +3698,7 @@
         <v>42.36</v>
       </c>
       <c r="I75" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3.35</v>
+        <v>3.445</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4.5475</v>
+        <v>4.298</v>
       </c>
       <c r="G76" t="n">
         <v>3.69</v>
@@ -3746,11 +3746,11 @@
         <v>5.5</v>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>38.37</v>
+        <v>36.14</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>79.875</v>
+        <v>75.77500000000001</v>
       </c>
       <c r="G77" t="n">
         <v>14</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>115.03</v>
+        <v>108.39</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>42.37</v>
+        <v>39.425</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.995</v>
+        <v>2.5477</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>5.5</v>
+        <v>5.61111</v>
       </c>
       <c r="G80" t="n">
         <v>3.3</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6.59</v>
+        <v>5.395</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>40</v>
+        <v>37.86</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>51.31818</v>
+        <v>51.59091</v>
       </c>
       <c r="G82" t="n">
         <v>33</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>365.065</v>
+        <v>392.32</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>364.014</v>
+        <v>396.12</v>
       </c>
       <c r="G83" t="n">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="H83" t="n">
         <v>475</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>187.974</v>
+        <v>215.97</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>184.1884</v>
+        <v>193.02959</v>
       </c>
       <c r="G84" t="n">
         <v>130</v>
@@ -4106,7 +4106,7 @@
         <v>275</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>83.47</v>
+        <v>76.52</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>116.25735</v>
+        <v>114.704285</v>
       </c>
       <c r="G85" t="n">
-        <v>85.16468</v>
+        <v>85.30834</v>
       </c>
       <c r="H85" t="n">
-        <v>171.74367</v>
+        <v>150.50607</v>
       </c>
       <c r="I85" t="n">
         <v>34</v>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>178.615</v>
+        <v>182.745</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>143.11</v>
+        <v>151.25</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4229,16 +4229,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>220.73685</v>
+        <v>226</v>
       </c>
       <c r="G87" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="H87" t="n">
         <v>450</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9.185</v>
+        <v>8.755000000000001</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>11.701622</v>
+        <v>11.195689</v>
       </c>
       <c r="G88" t="n">
-        <v>7.7563353</v>
+        <v>6.9175434</v>
       </c>
       <c r="H88" t="n">
-        <v>14.063471</v>
+        <v>13.966519</v>
       </c>
       <c r="I88" t="n">
         <v>15</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26.165</v>
+        <v>24.87</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>44.27</v>
+        <v>47.705</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>42.37</v>
+        <v>38.58</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6.17</v>
+        <v>4.9001</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6.78</v>
+        <v>6.68</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>12.429201</v>
+        <v>12.037995</v>
       </c>
       <c r="G93" t="n">
-        <v>7.8400655</v>
+        <v>7.5933013</v>
       </c>
       <c r="H93" t="n">
-        <v>18.100048</v>
+        <v>17.530352</v>
       </c>
       <c r="I93" t="n">
         <v>5</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>17.865</v>
+        <v>18.895</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>32.40286</v>
+        <v>32.52091</v>
       </c>
       <c r="G94" t="n">
         <v>22</v>
@@ -4550,7 +4550,7 @@
         <v>45</v>
       </c>
       <c r="I94" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>96.815</v>
+        <v>85.09</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>116.08</v>
+        <v>116.28</v>
       </c>
       <c r="G95" t="n">
         <v>103</v>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5175</v>
+        <v>5045</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>43.5295</v>
+        <v>41.75</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4677,20 +4677,20 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>34.74167</v>
+        <v>38.27857</v>
       </c>
       <c r="G97" t="n">
         <v>31.25</v>
       </c>
       <c r="H97" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>161.465</v>
+        <v>157.745</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>161.61765</v>
+        <v>164.67647</v>
       </c>
       <c r="G98" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H98" t="n">
         <v>200</v>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>62.61</v>
+        <v>57.735</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>69.13043</v>
+        <v>69.22727</v>
       </c>
       <c r="G99" t="n">
         <v>55</v>
@@ -4782,7 +4782,7 @@
         <v>77</v>
       </c>
       <c r="I99" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>20.4</v>
+        <v>17.6582</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>23.31818</v>
+        <v>23.95455</v>
       </c>
       <c r="G100" t="n">
         <v>18</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>139.11</v>
+        <v>111.13</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>144.04762</v>
+        <v>143.7619</v>
       </c>
       <c r="G101" t="n">
         <v>119</v>
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.21</v>
+        <v>10.24</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>38.315</v>
+        <v>35.825</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>50.51765</v>
+        <v>45.62778</v>
       </c>
       <c r="G103" t="n">
         <v>23</v>
@@ -4966,7 +4966,7 @@
         <v>94</v>
       </c>
       <c r="I103" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>144.24</v>
+        <v>104.96</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>129.14285</v>
+        <v>128.57143</v>
       </c>
       <c r="G104" t="n">
         <v>94</v>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>105.52</v>
+        <v>104.765</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>127.725</v>
+        <v>126.775</v>
       </c>
       <c r="G105" t="n">
         <v>81</v>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>8255</v>
+        <v>7965</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>16140</v>
+        <v>16560</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6.965</v>
+        <v>7.3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5189,16 +5189,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>6.623</v>
+        <v>7.49667</v>
       </c>
       <c r="G108" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="H108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>116.17</v>
+        <v>103.22</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>86.40000000000001</v>
+        <v>119.705</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>114.87805</v>
+        <v>116.37209</v>
       </c>
       <c r="G110" t="n">
         <v>75</v>
@@ -5282,11 +5282,11 @@
         <v>200</v>
       </c>
       <c r="I110" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>19.5</v>
+        <v>17.195</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>23.375</v>
+        <v>23.075</v>
       </c>
       <c r="G111" t="n">
         <v>17</v>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>414</v>
+        <v>385.05</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>462.37326</v>
+        <v>458.50256</v>
       </c>
       <c r="G112" t="n">
-        <v>400.6941</v>
+        <v>403.3746</v>
       </c>
       <c r="H112" t="n">
-        <v>533.89044</v>
+        <v>517.08636</v>
       </c>
       <c r="I112" t="n">
         <v>14</v>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>80.69</v>
+        <v>72.02</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5417,20 +5417,20 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>87.03846</v>
+        <v>88.33333</v>
       </c>
       <c r="G113" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H113" t="n">
         <v>105</v>
       </c>
       <c r="I113" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>203.52</v>
+        <v>265.0634</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -5465,16 +5465,16 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>279.62363</v>
+        <v>290.9704</v>
       </c>
       <c r="G114" t="n">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="H114" t="n">
         <v>400</v>
       </c>
       <c r="I114" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>19.425</v>
+        <v>17.575</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>20.72537</v>
+        <v>22.18614</v>
       </c>
       <c r="G115" t="n">
-        <v>16.67612</v>
+        <v>19.05842</v>
       </c>
       <c r="H115" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="I115" t="n">
         <v>3</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>17.24</v>
+        <v>16.7916</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>81.55</v>
+        <v>86.13</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>144.45714</v>
+        <v>141.57895</v>
       </c>
       <c r="G117" t="n">
         <v>39</v>
@@ -5606,7 +5606,7 @@
         <v>317</v>
       </c>
       <c r="I117" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>79.98999999999999</v>
+        <v>72.98</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>98.34999999999999</v>
+        <v>98.36357</v>
       </c>
       <c r="G118" t="n">
         <v>75</v>
@@ -5654,7 +5654,7 @@
         <v>125</v>
       </c>
       <c r="I118" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>157.01</v>
+        <v>150.21</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>15.14</v>
+        <v>13.225</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -5741,13 +5741,13 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>16.632</v>
+        <v>16.696</v>
       </c>
       <c r="G120" t="n">
         <v>12</v>
       </c>
       <c r="H120" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I120" t="n">
         <v>25</v>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>44.22</v>
+        <v>40.5301</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>72.575</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>32.6499</v>
+        <v>32.4699</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>23.85</v>
+        <v>20.85</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>26.46842</v>
+        <v>26.77222</v>
       </c>
       <c r="G124" t="n">
         <v>17</v>
@@ -5906,7 +5906,7 @@
         <v>35</v>
       </c>
       <c r="I124" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>29.855</v>
+        <v>23.99</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -5945,13 +5945,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>35.93</v>
+        <v>34.055</v>
       </c>
       <c r="G125" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I125" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>26.23</v>
+        <v>24.365</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>28.70652</v>
+        <v>29.05208</v>
       </c>
       <c r="G126" t="n">
         <v>20</v>
@@ -6002,7 +6002,7 @@
         <v>36</v>
       </c>
       <c r="I126" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>171.955</v>
+        <v>166.51</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>79.345</v>
+        <v>63.45</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -6077,20 +6077,20 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>113.88258</v>
+        <v>111.440125</v>
       </c>
       <c r="G128" t="n">
-        <v>83.85955</v>
+        <v>83.22696000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>150.0595</v>
+        <v>148.73073</v>
       </c>
       <c r="I128" t="n">
         <v>9</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>138.25</v>
+        <v>141.93</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>63.8</v>
+        <v>77.7901</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>63.35714</v>
+        <v>68.55556</v>
       </c>
       <c r="G130" t="n">
         <v>35</v>
@@ -6170,7 +6170,7 @@
         <v>100</v>
       </c>
       <c r="I130" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>82.913</v>
+        <v>75.5585</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>98.38889</v>
+        <v>98.15788999999999</v>
       </c>
       <c r="G131" t="n">
         <v>55</v>
@@ -6218,7 +6218,7 @@
         <v>114</v>
       </c>
       <c r="I131" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>83.895</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>61.565</v>
+        <v>53.655</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>68.21250000000001</v>
+        <v>67.2625</v>
       </c>
       <c r="G133" t="n">
-        <v>61.5</v>
+        <v>59</v>
       </c>
       <c r="H133" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I133" t="n">
         <v>20</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>77.5</v>
+        <v>83.0038</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>105.1875</v>
+        <v>102.9375</v>
       </c>
       <c r="G134" t="n">
         <v>50</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>85.785</v>
+        <v>80.36</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>82.005</v>
+        <v>80.675</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1660</v>
+        <v>1802.005</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2146.371</v>
+        <v>2093.704</v>
       </c>
       <c r="G137" t="n">
-        <v>897.9109</v>
+        <v>869.64935</v>
       </c>
       <c r="H137" t="n">
-        <v>2882.2273</v>
+        <v>2784.762</v>
       </c>
       <c r="I137" t="n">
         <v>16</v>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>107.1</v>
+        <v>102.57</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>95.68000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>35.405</v>
+        <v>39.8243</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -6581,16 +6581,16 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>78.3125</v>
+        <v>77.69444</v>
       </c>
       <c r="G140" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H140" t="n">
         <v>131</v>
       </c>
       <c r="I140" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>15380</v>
+        <v>16820</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>209.47</v>
+        <v>208.24</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10.25</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -6705,20 +6705,20 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>19.360693</v>
+        <v>16.307878</v>
       </c>
       <c r="G143" t="n">
-        <v>19.360693</v>
+        <v>13.756724</v>
       </c>
       <c r="H143" t="n">
-        <v>19.360693</v>
+        <v>18.85903</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>236.22</v>
+        <v>227.77</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>13.275</v>
+        <v>13.055</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -6789,10 +6789,10 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>18.5</v>
+        <v>17.01304</v>
       </c>
       <c r="G145" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H145" t="n">
         <v>25</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>543.115</v>
+        <v>491.24</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -6837,16 +6837,16 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>613.05566</v>
+        <v>593.80927</v>
       </c>
       <c r="G146" t="n">
-        <v>423.26602</v>
+        <v>409.94382</v>
       </c>
       <c r="H146" t="n">
-        <v>725.59894</v>
+        <v>702.76086</v>
       </c>
       <c r="I146" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>231.92</v>
+        <v>292.7</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>286.44104</v>
+        <v>288.705</v>
       </c>
       <c r="G147" t="n">
         <v>125</v>
@@ -6894,7 +6894,7 @@
         <v>500</v>
       </c>
       <c r="I147" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>159.84</v>
+        <v>157.95</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>173.98</v>
+        <v>167.7</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>190.45</v>
+        <v>203.7675</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -7005,16 +7005,16 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>241.81519</v>
+        <v>242.20724</v>
       </c>
       <c r="G150" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H150" t="n">
         <v>289</v>
       </c>
       <c r="I150" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>241.63</v>
+        <v>232.8057</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>399.4102</v>
+        <v>382.34</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>52.505</v>
+        <v>53.09</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -7125,16 +7125,16 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>59.8103</v>
+        <v>56.91719</v>
       </c>
       <c r="G153" t="n">
         <v>36</v>
       </c>
       <c r="H153" t="n">
-        <v>147.39</v>
+        <v>80</v>
       </c>
       <c r="I153" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>28.742</v>
+        <v>28.235</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>28.60577</v>
+        <v>28.875</v>
       </c>
       <c r="G154" t="n">
         <v>25</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>136.11</v>
+        <v>139.14</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>217.42105</v>
+        <v>212.78947</v>
       </c>
       <c r="G155" t="n">
         <v>106</v>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>14.655</v>
+        <v>12.885</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>18.78182</v>
+        <v>18.63636</v>
       </c>
       <c r="G156" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H156" t="n">
         <v>23</v>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>275.575</v>
+        <v>258.59</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -7317,13 +7317,13 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>348.304</v>
+        <v>342.982</v>
       </c>
       <c r="G157" t="n">
         <v>290</v>
       </c>
       <c r="H157" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
       <c r="I157" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>58.4</v>
+        <v>54.795</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>43.915</v>
+        <v>44.13</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -7401,16 +7401,16 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>47.62778</v>
+        <v>50.79211</v>
       </c>
       <c r="G159" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H159" t="n">
-        <v>64</v>
+        <v>72.95</v>
       </c>
       <c r="I159" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>290.44</v>
+        <v>239.165</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -7449,16 +7449,16 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>272.22354</v>
+        <v>275.06375</v>
       </c>
       <c r="G160" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H160" t="n">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="I160" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>183.07</v>
+        <v>162.19</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>243.375</v>
+        <v>243.52</v>
       </c>
       <c r="G161" t="n">
         <v>169</v>
@@ -7506,11 +7506,11 @@
         <v>300</v>
       </c>
       <c r="I161" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>91.23</v>
+        <v>83.155</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>18.355</v>
+        <v>13.235</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>13.43625</v>
+        <v>15.49882</v>
       </c>
       <c r="G163" t="n">
-        <v>10.98</v>
+        <v>10</v>
       </c>
       <c r="H163" t="n">
+        <v>23</v>
+      </c>
+      <c r="I163" t="n">
         <v>17</v>
       </c>
-      <c r="I163" t="n">
-        <v>16</v>
-      </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>77.16</v>
+        <v>72.505</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>181.209</v>
+        <v>187.16</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>197.58862</v>
+        <v>207.34688</v>
       </c>
       <c r="G165" t="n">
         <v>95</v>
@@ -7674,7 +7674,7 @@
         <v>330</v>
       </c>
       <c r="I165" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>110.99</v>
+        <v>109.815</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>35.555</v>
+        <v>33.885</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>35.36</v>
+        <v>33.855</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>542.6</v>
+        <v>610.88</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>323.4</v>
+        <v>339.195</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -7861,20 +7861,20 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>327.85</v>
+        <v>425.14166</v>
       </c>
       <c r="G170" t="n">
         <v>110</v>
       </c>
       <c r="H170" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="I170" t="n">
         <v>48</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>106.635</v>
+        <v>94.5</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>112.22581</v>
+        <v>111.83333</v>
       </c>
       <c r="G171" t="n">
         <v>81</v>
@@ -7918,7 +7918,7 @@
         <v>143</v>
       </c>
       <c r="I171" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>50.75</v>
+        <v>45.175</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>65.90000000000001</v>
+        <v>64.77500000000001</v>
       </c>
       <c r="G172" t="n">
         <v>53</v>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>321.83</v>
+        <v>327.79</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -8005,13 +8005,13 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>324.45282</v>
+        <v>328.09384</v>
       </c>
       <c r="G173" t="n">
         <v>215</v>
       </c>
       <c r="H173" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I173" t="n">
         <v>39</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2.935</v>
+        <v>2.885</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3.3396</v>
+        <v>3.345</v>
       </c>
       <c r="G174" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H174" t="n">
         <v>4</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>129.315</v>
+        <v>156.535</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -8105,16 +8105,16 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>225.14285</v>
+        <v>229.86667</v>
       </c>
       <c r="G175" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H175" t="n">
         <v>435</v>
       </c>
       <c r="I175" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>30.25</v>
+        <v>27.145</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>34.6875</v>
+        <v>33.8125</v>
       </c>
       <c r="G176" t="n">
         <v>29</v>
       </c>
       <c r="H176" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I176" t="n">
         <v>16</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>18.32</v>
+        <v>17.99</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>29.205</v>
+        <v>29.08</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>31.23077</v>
+        <v>31.15385</v>
       </c>
       <c r="G178" t="n">
         <v>23</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>84.73</v>
+        <v>84.37</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>566.3049999999999</v>
+        <v>727.0599999999999</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>754.77405</v>
+        <v>793.90735</v>
       </c>
       <c r="G180" t="n">
         <v>580</v>
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>218.42</v>
+        <v>207.97</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>762.3209000000001</v>
+        <v>760.5700000000001</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>178.515</v>
+        <v>158.865</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>205.5238</v>
+        <v>204.09525</v>
       </c>
       <c r="G183" t="n">
         <v>170</v>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>95.62</v>
+        <v>85.7218</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -8489,16 +8489,16 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>148.82843</v>
+        <v>145.96782</v>
       </c>
       <c r="G184" t="n">
-        <v>80.25991</v>
+        <v>80.39530000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>206.63457</v>
+        <v>206.98314</v>
       </c>
       <c r="I184" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>28.045</v>
+        <v>26.395</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -8537,13 +8537,13 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>39.717564</v>
+        <v>39.47159</v>
       </c>
       <c r="G185" t="n">
-        <v>25.128614</v>
+        <v>25.171003</v>
       </c>
       <c r="H185" t="n">
-        <v>54.76781</v>
+        <v>53.363186</v>
       </c>
       <c r="I185" t="n">
         <v>35</v>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>14320</v>
+        <v>13730</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>140.62</v>
+        <v>126.195</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G187" t="n">
         <v>124</v>
       </c>
       <c r="H187" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I187" t="n">
         <v>22</v>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>7.8</v>
+        <v>8.315</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -8673,13 +8673,13 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>8.8375</v>
+        <v>8.875</v>
       </c>
       <c r="G188" t="n">
         <v>6.1</v>
       </c>
       <c r="H188" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="I188" t="n">
         <v>8</v>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>9.470000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>197.105</v>
+        <v>232.05</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>286.6875</v>
+        <v>283.57895</v>
       </c>
       <c r="G190" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="H190" t="n">
         <v>415</v>
       </c>
       <c r="I190" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>strong_buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>62.355</v>
+        <v>53.475</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -8817,20 +8817,20 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>68.77273</v>
+        <v>68.61905</v>
       </c>
       <c r="G191" t="n">
         <v>62</v>
       </c>
       <c r="H191" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I191" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>102.76</v>
+        <v>92.0231</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>104.09222</v>
+        <v>104.42556</v>
       </c>
       <c r="G192" t="n">
         <v>88</v>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>62.365</v>
+        <v>70.44</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>112.64706</v>
+        <v>109.36842</v>
       </c>
       <c r="G193" t="n">
         <v>64</v>
@@ -8922,11 +8922,11 @@
         <v>150</v>
       </c>
       <c r="I193" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>97.43000000000001</v>
+        <v>103.53</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>67.27</v>
+        <v>66.345</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>10.91</v>
+        <v>10.41</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>10.7975</v>
+        <v>10.85</v>
       </c>
       <c r="G196" t="n">
-        <v>9.789999999999999</v>
+        <v>10</v>
       </c>
       <c r="H196" t="n">
         <v>12</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>189.905</v>
+        <v>187.74</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -9081,20 +9081,20 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>203.8</v>
+        <v>208.13333</v>
       </c>
       <c r="G197" t="n">
         <v>175</v>
       </c>
       <c r="H197" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I197" t="n">
         <v>15</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>44.31</v>
+        <v>39.1</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>182.13</v>
+        <v>158.19</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -9165,16 +9165,16 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>176.75641</v>
+        <v>184.35</v>
       </c>
       <c r="G199" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H199" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I199" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>170.68</v>
+        <v>163.4999</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>185.57059</v>
+        <v>186.98334</v>
       </c>
       <c r="G200" t="n">
         <v>120</v>
@@ -9222,7 +9222,7 @@
         <v>219</v>
       </c>
       <c r="I200" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>60.719</v>
+        <v>57.085</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -9261,16 +9261,16 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>66.82608999999999</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="G201" t="n">
         <v>55</v>
       </c>
       <c r="H201" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I201" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>5.365</v>
+        <v>5.425</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>7.38333</v>
+        <v>7.39429</v>
       </c>
       <c r="G202" t="n">
         <v>5</v>
@@ -9318,7 +9318,7 @@
         <v>16</v>
       </c>
       <c r="I202" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>87.12</v>
+        <v>79.11</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>100.23913</v>
+        <v>100.54348</v>
       </c>
       <c r="G203" t="n">
         <v>90</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>206.43</v>
+        <v>186.98</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>274.84616</v>
+        <v>273.42307</v>
       </c>
       <c r="G204" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H204" t="n">
         <v>305</v>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>209.66</v>
+        <v>206.21</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -9453,13 +9453,13 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>218.29167</v>
+        <v>224.20833</v>
       </c>
       <c r="G205" t="n">
         <v>175</v>
       </c>
       <c r="H205" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I205" t="n">
         <v>24</v>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>86.14</v>
+        <v>77.39</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -9501,16 +9501,16 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>101.19231</v>
+        <v>104.21739</v>
       </c>
       <c r="G206" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="H206" t="n">
         <v>132</v>
       </c>
       <c r="I206" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>396.995</v>
+        <v>363.77</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -9549,16 +9549,16 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>475.23077</v>
+        <v>481.72</v>
       </c>
       <c r="G207" t="n">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="H207" t="n">
         <v>529</v>
       </c>
       <c r="I207" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>18180</v>
+        <v>15930</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>669.42</v>
+        <v>662.295</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -9637,16 +9637,16 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>666.71136</v>
+        <v>691.8339</v>
       </c>
       <c r="G209" t="n">
         <v>500</v>
       </c>
       <c r="H209" t="n">
-        <v>804</v>
+        <v>813.1799999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>113.285</v>
+        <v>107.08</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -9685,13 +9685,13 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>187.12779</v>
+        <v>185.5814</v>
       </c>
       <c r="G210" t="n">
-        <v>95.19119999999999</v>
+        <v>95.351776</v>
       </c>
       <c r="H210" t="n">
-        <v>238.1918</v>
+        <v>238.5936</v>
       </c>
       <c r="I210" t="n">
         <v>39</v>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>457.8686</v>
+        <v>610.165</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>613.8449000000001</v>
+        <v>618.508</v>
       </c>
       <c r="G211" t="n">
         <v>365</v>
@@ -9742,7 +9742,7 @@
         <v>1250</v>
       </c>
       <c r="I211" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>82.01000000000001</v>
+        <v>77.315</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>90.30768999999999</v>
+        <v>90.83333</v>
       </c>
       <c r="G212" t="n">
         <v>78</v>
@@ -9790,7 +9790,7 @@
         <v>100</v>
       </c>
       <c r="I212" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>13.9464</v>
+        <v>12.075</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -9829,16 +9829,16 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>15.726</v>
+        <v>16.03</v>
       </c>
       <c r="G213" t="n">
-        <v>11</v>
+        <v>12.8</v>
       </c>
       <c r="H213" t="n">
         <v>20</v>
       </c>
       <c r="I213" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>200.35</v>
+        <v>171.825</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>275.30466</v>
+        <v>275.87134</v>
       </c>
       <c r="G214" t="n">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="H214" t="n">
         <v>402</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>43.94</v>
+        <v>40.29</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>52.15867</v>
+        <v>51.70438</v>
       </c>
       <c r="G215" t="n">
         <v>29</v>
@@ -9934,7 +9934,7 @@
         <v>63</v>
       </c>
       <c r="I215" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>163.1403</v>
+        <v>183.71</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>193.1</v>
+        <v>194.13333</v>
       </c>
       <c r="G216" t="n">
         <v>100</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1543.01</v>
+        <v>1743.21</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2125.087</v>
+        <v>2136.5417</v>
       </c>
       <c r="G217" t="n">
         <v>1000</v>
@@ -10030,7 +10030,7 @@
         <v>3600</v>
       </c>
       <c r="I217" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>269.01</v>
+        <v>260.55</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>272.5</v>
+        <v>279.27274</v>
       </c>
       <c r="G218" t="n">
         <v>190</v>
       </c>
       <c r="H218" t="n">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="I218" t="n">
         <v>22</v>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>73.95</v>
+        <v>64.8</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -10117,20 +10117,20 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>98.681175</v>
+        <v>91.36378000000001</v>
       </c>
       <c r="G219" t="n">
-        <v>82.13291</v>
+        <v>75.849236</v>
       </c>
       <c r="H219" t="n">
-        <v>123.48404</v>
+        <v>114.03675</v>
       </c>
       <c r="I219" t="n">
         <v>12</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>109.52</v>
+        <v>108.37</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -10165,16 +10165,16 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>137.73914</v>
+        <v>136.16</v>
       </c>
       <c r="G220" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H220" t="n">
         <v>170</v>
       </c>
       <c r="I220" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>106.665</v>
+        <v>109.77</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -10213,10 +10213,10 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>161.41304</v>
+        <v>156.34782</v>
       </c>
       <c r="G221" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H221" t="n">
         <v>203</v>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>10.85</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>197.245</v>
+        <v>182.54</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>214.97571</v>
+        <v>215.96358</v>
       </c>
       <c r="G223" t="n">
         <v>87</v>
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>132.875</v>
+        <v>128.615</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -10349,10 +10349,10 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>170.0001</v>
+        <v>169.625</v>
       </c>
       <c r="G224" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H224" t="n">
         <v>186</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>59.45</v>
+        <v>48.495</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -10397,13 +10397,13 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>61.93103</v>
+        <v>62.51724</v>
       </c>
       <c r="G225" t="n">
         <v>43</v>
       </c>
       <c r="H225" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I225" t="n">
         <v>29</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>434.555</v>
+        <v>411.155</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -10445,20 +10445,20 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>388.48276</v>
+        <v>390.9438</v>
       </c>
       <c r="G226" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H226" t="n">
-        <v>457</v>
+        <v>500</v>
       </c>
       <c r="I226" t="n">
         <v>29</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>219.918</v>
+        <v>265.05</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -10493,16 +10493,16 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>229.30612</v>
+        <v>235.67</v>
       </c>
       <c r="G227" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H227" t="n">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="I227" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>147.66</v>
+        <v>143.575</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>262.16</v>
+        <v>231.475</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -10589,16 +10589,16 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>315.3871</v>
+        <v>297.2069</v>
       </c>
       <c r="G229" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H229" t="n">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="I229" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>7.96</v>
+        <v>6.725</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>50.615</v>
+        <v>45.945</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>96.53</v>
+        <v>87.55500000000001</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1.0691</v>
+        <v>1.075</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="G233" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H233" t="n">
         <v>1.5</v>
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>282.06</v>
+        <v>278.68</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>217.995</v>
+        <v>225.075</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -10857,10 +10857,10 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>236.22</v>
+        <v>238.18195</v>
       </c>
       <c r="G235" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H235" t="n">
         <v>300</v>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>89.12</v>
+        <v>86.16500000000001</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>94.69565</v>
+        <v>94.65217</v>
       </c>
       <c r="G236" t="n">
         <v>75</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>257.89</v>
+        <v>232.595</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>266.48364</v>
+        <v>281.0783</v>
       </c>
       <c r="G237" t="n">
         <v>160</v>
@@ -10962,7 +10962,7 @@
         <v>475</v>
       </c>
       <c r="I237" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>37.135</v>
+        <v>31.895</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>43.12</v>
+        <v>43.44</v>
       </c>
       <c r="G238" t="n">
         <v>29</v>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>19.925</v>
+        <v>20.8451</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>22.0275</v>
+        <v>22.89286</v>
       </c>
       <c r="G239" t="n">
         <v>17.4</v>
       </c>
       <c r="H239" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I239" t="n">
         <v>14</v>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>163.835</v>
+        <v>163.65</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>169.68182</v>
+        <v>173.04546</v>
       </c>
       <c r="G240" t="n">
         <v>142</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>322.68</v>
+        <v>280.115</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>377.5</v>
+        <v>377.1875</v>
       </c>
       <c r="G241" t="n">
         <v>310</v>
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>14.925</v>
+        <v>15.62</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>28.8125</v>
+        <v>28.525</v>
       </c>
       <c r="G242" t="n">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="H242" t="n">
         <v>40</v>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>4.665</v>
+        <v>4.715</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -11241,20 +11241,20 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>5.5665975</v>
+        <v>5.5822206</v>
       </c>
       <c r="G243" t="n">
-        <v>5.0090327</v>
+        <v>4.931913</v>
       </c>
       <c r="H243" t="n">
-        <v>6.095453</v>
+        <v>6.369774</v>
       </c>
       <c r="I243" t="n">
         <v>5</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>415.34</v>
+        <v>454.97</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>554.45483</v>
+        <v>552.2594</v>
       </c>
       <c r="G244" t="n">
         <v>440</v>
@@ -11298,7 +11298,7 @@
         <v>700</v>
       </c>
       <c r="I244" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>69.861</v>
+        <v>66.89</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>199.205</v>
+        <v>182.385</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -11385,10 +11385,10 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>231.57802</v>
+        <v>234.07802</v>
       </c>
       <c r="G246" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="H246" t="n">
         <v>239.31209</v>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>780.015</v>
+        <v>823.87</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>2.89</v>
+        <v>2.9612</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>36.735</v>
+        <v>36.775</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1944.04</v>
+        <v>1685.085</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2256.5417</v>
+        <v>2266.0928</v>
       </c>
       <c r="G250" t="n">
         <v>1750</v>
@@ -11574,11 +11574,11 @@
         <v>2800</v>
       </c>
       <c r="I250" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>14.75</v>
+        <v>14.92</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1169.405</v>
+        <v>1143</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -11661,10 +11661,10 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>1315.0406</v>
+        <v>1328.8337</v>
       </c>
       <c r="G252" t="n">
-        <v>850</v>
+        <v>930</v>
       </c>
       <c r="H252" t="n">
         <v>1600</v>
@@ -11701,7 +11701,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>22.14</v>
+        <v>17.8</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -11709,20 +11709,20 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>26</v>
+        <v>25.125</v>
       </c>
       <c r="G253" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H253" t="n">
         <v>30</v>
       </c>
       <c r="I253" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>74.145</v>
+        <v>68.56100000000001</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -11757,13 +11757,13 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>72.04545</v>
+        <v>72.77273</v>
       </c>
       <c r="G254" t="n">
         <v>30</v>
       </c>
       <c r="H254" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I254" t="n">
         <v>22</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>358.67</v>
+        <v>356.3036</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>390.09283</v>
+        <v>395.83212</v>
       </c>
       <c r="G255" t="n">
         <v>125</v>
@@ -11814,7 +11814,7 @@
         <v>600</v>
       </c>
       <c r="I255" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>503.33</v>
+        <v>513.595</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -11853,10 +11853,10 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>569.4537</v>
+        <v>578.41516</v>
       </c>
       <c r="G256" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="H256" t="n">
         <v>870</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>231.05</v>
+        <v>225.27</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -11901,16 +11901,16 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>244.91217</v>
+        <v>240.59</v>
       </c>
       <c r="G257" t="n">
         <v>174</v>
       </c>
       <c r="H257" t="n">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="I257" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>67.2</v>
+        <v>61.4899</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -11949,13 +11949,13 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>66.20833</v>
+        <v>66.70833</v>
       </c>
       <c r="G258" t="n">
         <v>40</v>
       </c>
       <c r="H258" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I258" t="n">
         <v>24</v>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1790</v>
+        <v>1695</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>260.47</v>
+        <v>259.155</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>276.5862</v>
+        <v>278.85715</v>
       </c>
       <c r="G260" t="n">
         <v>200</v>
@@ -12046,7 +12046,7 @@
         <v>328</v>
       </c>
       <c r="I260" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>588.765</v>
+        <v>549.1900000000001</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>670.91895</v>
+        <v>666.7138</v>
       </c>
       <c r="G261" t="n">
         <v>550</v>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>65.41</v>
+        <v>59.325</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -12133,20 +12133,20 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>74.09819</v>
+        <v>71.636505</v>
       </c>
       <c r="G262" t="n">
-        <v>70.1799</v>
+        <v>67.963356</v>
       </c>
       <c r="H262" t="n">
-        <v>77.41179</v>
+        <v>75.30628</v>
       </c>
       <c r="I262" t="n">
         <v>4</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>328.29</v>
+        <v>299.99</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -12181,16 +12181,16 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>375.9556</v>
+        <v>377.91208</v>
       </c>
       <c r="G263" t="n">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="H263" t="n">
         <v>450</v>
       </c>
       <c r="I263" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>150.03</v>
+        <v>143.96</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>148.73077</v>
+        <v>155.76</v>
       </c>
       <c r="G265" t="n">
         <v>105</v>
@@ -12286,7 +12286,7 @@
         <v>186</v>
       </c>
       <c r="I265" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>209.6</v>
+        <v>185.26</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>234.81818</v>
+        <v>234.13635</v>
       </c>
       <c r="G266" t="n">
         <v>200</v>
@@ -12365,7 +12365,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>326.78</v>
+        <v>287.69</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>356.37125</v>
+        <v>356.30356</v>
       </c>
       <c r="G267" t="n">
         <v>160</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>529.58</v>
+        <v>506.72</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>945.8099999999999</v>
+        <v>919.59</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1077.3143</v>
+        <v>1057.9429</v>
       </c>
       <c r="G269" t="n">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="H269" t="n">
         <v>1315</v>
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>57.61</v>
+        <v>53.14</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>90.97</v>
+        <v>84.16</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>106.28571</v>
+        <v>107.57143</v>
       </c>
       <c r="G271" t="n">
         <v>76</v>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>378.855</v>
+        <v>358.65</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>108.13</v>
+        <v>94.985</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>118.6</v>
+        <v>116.2</v>
       </c>
       <c r="G273" t="n">
         <v>90</v>
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>291.74</v>
+        <v>277.8</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>36640</v>
+        <v>36700</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>21450</v>
+        <v>20900</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>612.5</v>
+        <v>664.0549999999999</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -12801,13 +12801,13 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>631.4231</v>
+        <v>652.8461</v>
       </c>
       <c r="G277" t="n">
         <v>520</v>
       </c>
       <c r="H277" t="n">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="I277" t="n">
         <v>26</v>
@@ -12841,7 +12841,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>37200</v>
+        <v>34420</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>356.67</v>
+        <v>330.1457</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -12889,20 +12889,20 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>374.57144</v>
+        <v>375.8095</v>
       </c>
       <c r="G279" t="n">
         <v>305</v>
       </c>
       <c r="H279" t="n">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="I279" t="n">
         <v>21</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>707.6903</v>
+        <v>737.835</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>64.59</v>
+        <v>62.3484</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>132.71</v>
+        <v>125.615</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -13009,10 +13009,10 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>154.5</v>
+        <v>154.9</v>
       </c>
       <c r="G282" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H282" t="n">
         <v>176</v>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>30.2275</v>
+        <v>32.015</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>29.45625</v>
+        <v>29.66471</v>
       </c>
       <c r="G283" t="n">
         <v>19</v>
@@ -13066,11 +13066,11 @@
         <v>72</v>
       </c>
       <c r="I283" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>557.65</v>
+        <v>506.7625</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>632.9474</v>
+        <v>636.7368</v>
       </c>
       <c r="G284" t="n">
         <v>503</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>490.035</v>
+        <v>446.23</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>526.8182</v>
+        <v>526.9091</v>
       </c>
       <c r="G285" t="n">
         <v>476</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>104.88</v>
+        <v>105.765</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -13201,10 +13201,10 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>116.14815</v>
+        <v>116.11111</v>
       </c>
       <c r="G286" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H286" t="n">
         <v>145</v>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>110.58</v>
+        <v>97.66</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>120.2</v>
+        <v>120.2636</v>
       </c>
       <c r="G287" t="n">
         <v>103</v>
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>3.065</v>
+        <v>3.39</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>6.45</v>
+        <v>6.54545</v>
       </c>
       <c r="G288" t="n">
         <v>4.5</v>
@@ -13306,11 +13306,11 @@
         <v>10</v>
       </c>
       <c r="I288" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>942</v>
+        <v>1044.11</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>1513.409</v>
+        <v>1533.8043</v>
       </c>
       <c r="G289" t="n">
         <v>361</v>
@@ -13354,7 +13354,7 @@
         <v>2200</v>
       </c>
       <c r="I289" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>14.595</v>
+        <v>13.2201</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -13433,7 +13433,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>75.8535</v>
+        <v>82.17</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -13441,16 +13441,16 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>161.77779</v>
+        <v>157.09091</v>
       </c>
       <c r="G291" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="H291" t="n">
         <v>273</v>
       </c>
       <c r="I291" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>90.965</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>98.95</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G292" t="n">
         <v>87</v>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>40.05</v>
+        <v>42.68</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -13537,13 +13537,13 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>48.32441</v>
+        <v>48.97471</v>
       </c>
       <c r="G293" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H293" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I293" t="n">
         <v>34</v>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>147.8</v>
+        <v>147.2</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>157.40741</v>
+        <v>158.65385</v>
       </c>
       <c r="G294" t="n">
         <v>123</v>
@@ -13594,7 +13594,7 @@
         <v>180</v>
       </c>
       <c r="I294" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>291.25</v>
+        <v>286.22</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -13633,10 +13633,10 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>318</v>
+        <v>324.4</v>
       </c>
       <c r="G295" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="H295" t="n">
         <v>355</v>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>162.65</v>
+        <v>158.67</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>212.53636</v>
+        <v>212.17273</v>
       </c>
       <c r="G296" t="n">
         <v>184</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>93.59</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -13729,16 +13729,16 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>74.07143000000001</v>
+        <v>77.58333</v>
       </c>
       <c r="G297" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="H297" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I297" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>215.82</v>
+        <v>209.93</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>247.25</v>
+        <v>251.5</v>
       </c>
       <c r="G298" t="n">
         <v>177</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>123.325</v>
+        <v>111.125</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -13825,20 +13825,20 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>141.02937</v>
+        <v>144.8</v>
       </c>
       <c r="G299" t="n">
-        <v>110.47</v>
+        <v>125</v>
       </c>
       <c r="H299" t="n">
         <v>164</v>
       </c>
       <c r="I299" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -13865,7 +13865,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>92.89</v>
+        <v>95.205</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -13873,13 +13873,13 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>97.76667</v>
+        <v>103.74667</v>
       </c>
       <c r="G300" t="n">
-        <v>81.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="H300" t="n">
-        <v>120.6</v>
+        <v>123</v>
       </c>
       <c r="I300" t="n">
         <v>15</v>
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>442.98</v>
+        <v>524.3</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>640.3143</v>
+        <v>638.94446</v>
       </c>
       <c r="G301" t="n">
         <v>358</v>
@@ -13930,7 +13930,7 @@
         <v>900</v>
       </c>
       <c r="I301" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>252.74</v>
+        <v>279.77</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>39.47</v>
+        <v>39.27</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>75.01000000000001</v>
+        <v>67.48399999999999</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>101.84913</v>
+        <v>100.77319</v>
       </c>
       <c r="G304" t="n">
         <v>70</v>
@@ -14062,7 +14062,7 @@
         <v>150</v>
       </c>
       <c r="I304" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>124.5</v>
+        <v>115.135</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>132.86714</v>
+        <v>137.7381</v>
       </c>
       <c r="G305" t="n">
         <v>67</v>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>383.8101</v>
+        <v>365.64</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -14149,10 +14149,10 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>413.77777</v>
+        <v>416.55557</v>
       </c>
       <c r="G306" t="n">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="H306" t="n">
         <v>485</v>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -14189,7 +14189,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>8.289999999999999</v>
+        <v>6.395</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -14197,16 +14197,16 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>12.049841</v>
+        <v>12.914381</v>
       </c>
       <c r="G307" t="n">
-        <v>9.448286</v>
+        <v>12.161726</v>
       </c>
       <c r="H307" t="n">
-        <v>14.213483</v>
+        <v>13.667036</v>
       </c>
       <c r="I307" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>206.57</v>
+        <v>197.33</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -14245,10 +14245,10 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>169.05853</v>
+        <v>171.44041</v>
       </c>
       <c r="G308" t="n">
-        <v>126.97628</v>
+        <v>138.33992</v>
       </c>
       <c r="H308" t="n">
         <v>275</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>143.83</v>
+        <v>136.7335</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>244.11761</v>
+        <v>237.97415</v>
       </c>
       <c r="G309" t="n">
         <v>110</v>
@@ -14302,7 +14302,7 @@
         <v>400</v>
       </c>
       <c r="I309" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>184.0701</v>
+        <v>188.8</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>191.68</v>
+        <v>195.56538</v>
       </c>
       <c r="G310" t="n">
         <v>80</v>
@@ -14350,7 +14350,7 @@
         <v>255</v>
       </c>
       <c r="I310" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>65.75</v>
+        <v>65.955</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>283.14</v>
+        <v>286.27</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -14429,20 +14429,20 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>290.2857</v>
+        <v>302</v>
       </c>
       <c r="G312" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H312" t="n">
         <v>370</v>
       </c>
       <c r="I312" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>42.06</v>
+        <v>32.22</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>87.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G313" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="H313" t="n">
         <v>135</v>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1015.2</v>
+        <v>890.38</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -14525,13 +14525,13 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>1141.65</v>
+        <v>1127.25</v>
       </c>
       <c r="G314" t="n">
         <v>730</v>
       </c>
       <c r="H314" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="I314" t="n">
         <v>20</v>
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>83.09999999999999</v>
+        <v>76.27500000000001</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>102.83</v>
+        <v>105.57</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>110.055</v>
+        <v>110.05</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>332.77</v>
+        <v>336.46</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>253.88</v>
+        <v>227.92</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -14741,16 +14741,16 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>337.128</v>
+        <v>334.36</v>
       </c>
       <c r="G319" t="n">
-        <v>256.56</v>
+        <v>255</v>
       </c>
       <c r="H319" t="n">
         <v>375</v>
       </c>
       <c r="I319" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>424.89</v>
+        <v>475.92</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -14789,20 +14789,20 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>544.9723</v>
+        <v>563.43384</v>
       </c>
       <c r="G320" t="n">
         <v>414.77</v>
       </c>
       <c r="H320" t="n">
-        <v>633</v>
+        <v>700</v>
       </c>
       <c r="I320" t="n">
         <v>26</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>strong_buy</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
